--- a/Resource/software_list/softwarelist.xlsx
+++ b/Resource/software_list/softwarelist.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\21005645\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\12 Claude-Cowork\03 Projects\20260623_WebsiteRobertoStructural\WebsiteRobertoStructural\Resource\software_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F17F9A-530A-42E9-BA09-B616B8F0D346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B80196-7657-4988-A220-FE2B8435D144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AD0764AB-2672-4561-8C21-7DE139ED03BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AD0764AB-2672-4561-8C21-7DE139ED03BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Python Tool" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="91">
   <si>
     <t>STT</t>
   </si>
@@ -72,9 +70,6 @@
     <t>RC DESIGN OUTPUT SAP2000</t>
   </si>
   <si>
-    <t>RCDesignSAP2000.exe</t>
-  </si>
-  <si>
     <t>VND</t>
   </si>
   <si>
@@ -87,36 +82,24 @@
     <t>SIDESWAY CHECK</t>
   </si>
   <si>
-    <t>SidewayCheck.exe</t>
-  </si>
-  <si>
     <t>V2.3</t>
   </si>
   <si>
     <t>DEFLECTION CHECK</t>
   </si>
   <si>
-    <t>DeflectionCheck.exe</t>
-  </si>
-  <si>
     <t>V2.5</t>
   </si>
   <si>
     <t>PILE CAPACITY CHECK</t>
   </si>
   <si>
-    <t>PileCapacityCheck.exe</t>
-  </si>
-  <si>
     <t>V1.2</t>
   </si>
   <si>
     <t>CRANE GIRDER DESIGN</t>
   </si>
   <si>
-    <t>CraneBeamDesign</t>
-  </si>
-  <si>
     <t>V2.0</t>
   </si>
   <si>
@@ -141,24 +124,15 @@
     <t>MONORAIL BEAM DESIGN</t>
   </si>
   <si>
-    <t>MonorailBeamDesign.exe</t>
-  </si>
-  <si>
     <t>WIND LOAD ON VERTICAL TANK</t>
   </si>
   <si>
-    <t>WindLoadOnVerticalTank.exe</t>
-  </si>
-  <si>
     <t>V2.1</t>
   </si>
   <si>
     <t>SEISMIC ON VERTICAL TANK</t>
   </si>
   <si>
-    <t>SeismicOnVerticalTank.exe</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -207,12 +181,6 @@
     <t>LDAssignment.exe</t>
   </si>
   <si>
-    <t>EmbpDesign.exe</t>
-  </si>
-  <si>
-    <t>RCCorbelDesign.exe</t>
-  </si>
-  <si>
     <t>Shallow FDN Design.exe</t>
   </si>
   <si>
@@ -241,45 +209,120 @@
   </si>
   <si>
     <t>Link Github Dowload</t>
-  </si>
-  <si>
-    <t>https://github.com/Roberto-0720/01_RCDesignSAP2000/releases/download/RCDesignSAP2000_V1.0/RCDesignSAP2000.zip
-https://github.com/Roberto-0720/01_RCDesignSAP2000/releases/latest/download/RCDesignSAP2000.zip</t>
   </si>
   <si>
     <t>https://github.com/Roberto-0720/05_GroundFloorDesign/releases/download/GRDS_V1.1/GRDS.zip
 https://github.com/Roberto-0720/05_GroundFloorDesign/releases/latest/download/GRDS.zip</t>
   </si>
   <si>
-    <t>https://github.com/Roberto-0720/02_Sidesway-Check/releases/download/SidewayCheck_V2.3/SidewayCheck.zip
-https://github.com/Roberto-0720/02_Sidesway-Check/releases/latest/download/SidewayCheck.zip</t>
-  </si>
-  <si>
-    <t>https://github.com/Roberto-0720/03_DeflectionCheck/releases/download/DeflectionCheck_V2.5/DeflectionCheck.zip
-https://github.com/Roberto-0720/03_DeflectionCheck/releases/latest/download/DeflectionCheck.zip</t>
-  </si>
-  <si>
-    <t>https://github.com/Roberto-0720/04_PileCapacityCheck/releases/download/PileCapacityCheck_V1.2/PileCapcityCheck.zip
-https://github.com/Roberto-0720/04_PileCapacityCheck/releases/latest/download/PileCapcityCheck.zip</t>
-  </si>
-  <si>
-    <t>https://github.com/Roberto-0720/10_SeismicOnVerTank/releases/download/SeismicOnVerTank_V2.1/SeismicOnVerticalTank.zip
-https://github.com/Roberto-0720/10_SeismicOnVerTank/releases/latest/download/SeismicOnVerticalTank.zip</t>
-  </si>
-  <si>
-    <t>https://github.com/Roberto-0720/09_WindLoadOnVerticalTank/releases/download/WindLoadOnVerTank_V2.1/WindLoadOnVerticalTank.zip
-https://github.com/Roberto-0720/09_WindLoadOnVerticalTank/releases/latest/download/WindLoadOnVerticalTank.zip</t>
-  </si>
-  <si>
-    <t>https://github.com/Roberto-0720/08_MonorailBeamDesgin/releases/download/Monorail_V1.2/Monorail.zip
-https://github.com/Roberto-0720/08_MonorailBeamDesgin/releases/latest/download/Monorail.zip</t>
-  </si>
-  <si>
     <t>https://github.com/Roberto-0720/07_SteelCad/releases/download/SteelCad_V1.0/SteelCad.zip
 https://github.com/Roberto-0720/07_SteelCad/releases/latest/download/SteelCad.zip</t>
   </si>
   <si>
     <t>On Going</t>
+  </si>
+  <si>
+    <t>Description Picture</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>RCD.exe</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/01_RCDesignSAP2000/releases/download/RCDesignSAP2000_V1.0/RCD.zip
+https://github.com/Roberto-0720/01_RCDesignSAP2000/releases/latest/download/RCD.zip</t>
+  </si>
+  <si>
+    <t>SWC.exe</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/02_Sidesway-Check/releases/download/SidewayCheck_V2.3/SWC.zip
+https://github.com/Roberto-0720/02_Sidesway-Check/releases/latest/download/SWC.zip</t>
+  </si>
+  <si>
+    <t>DEFC.exe</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/03_DeflectionCheck/releases/download/DeflectionCheck_V2.5/DEFC.zip
+https://github.com/Roberto-0720/03_DeflectionCheck/releases/latest/download/DEFC.zip</t>
+  </si>
+  <si>
+    <t>PCC.exe</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/04_PileCapacityCheck/releases/download/PileCapacityCheck_V1.2/PCC.zip
+https://github.com/Roberto-0720/04_PileCapacityCheck/releases/latest/download/PCC.zip</t>
+  </si>
+  <si>
+    <t>CBD.exe</t>
+  </si>
+  <si>
+    <t>MRD.exe</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/06_CraneGirderDesign/releases/download/CraneBeamDesign_V3.0/CBD.zip
+https://github.com/Roberto-0720/06_CraneGirderDesign/releases/latest/download/CBD.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/10_SeismicOnVerTank/releases/download/SeismicOnVerTank_V2.1/SLVT.zip
+https://github.com/Roberto-0720/10_SeismicOnVerTank/releases/latest/download/SLVT.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/08_MonorailBeamDesgin/releases/download/Monorail_V1.2/MRD.zip
+https://github.com/Roberto-0720/08_MonorailBeamDesgin/releases/latest/download/MRD.zip</t>
+  </si>
+  <si>
+    <t>WLVT.exe</t>
+  </si>
+  <si>
+    <t>SLVT.exe</t>
+  </si>
+  <si>
+    <t>EBPL.exe</t>
+  </si>
+  <si>
+    <t>COBL.exe</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/09_WindLoadOnVerticalTank/releases/download/WindLoadOnVerTank_V2.1/WLVT.zip
+https://github.com/Roberto-0720/09_WindLoadOnVerticalTank/releases/latest/download/WLVT.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/12_RCCorbel/releases/download/RCCorbel_V1.0/COBL.zip
+https://github.com/Roberto-0720/12_RCCorbel/releases/latest/download/COBL.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/11_EmbeddedPlate/releases/download/EmbeddedPlate_V1.0/EBPL.zip
+https://github.com/Roberto-0720/11_EmbeddedPlate/releases/latest/download/EBPL.zip</t>
+  </si>
+  <si>
+    <t>Building Name</t>
+  </si>
+  <si>
+    <t>Arch</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>MEP</t>
+  </si>
+  <si>
+    <t>Townhouse_01_5x14.5x4</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>AutoCad</t>
+  </si>
+  <si>
+    <t>Github</t>
+  </si>
+  <si>
+    <t>Villa_01_12x20x2.5</t>
   </si>
 </sst>
 </file>
@@ -287,7 +330,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0;\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;\-&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -347,10 +390,11 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="Cambria"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Symbol"/>
       <family val="1"/>
+      <charset val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -373,7 +417,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -396,12 +440,75 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -412,7 +519,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="5" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -427,7 +534,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="5" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -439,8 +546,26 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -782,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2825F4-381A-4176-BB68-B1332D84AD9D}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.77734375" style="1" customWidth="1"/>
@@ -793,12 +918,12 @@
     <col min="6" max="6" width="10.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="23.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="95.21875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="9" max="10" width="23.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="95.21875" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -815,22 +940,25 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -838,10 +966,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" s="9">
         <v>15</v>
@@ -850,30 +978,33 @@
         <v>350000</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>16</v>
       </c>
       <c r="E3" s="9">
         <v>5</v>
@@ -882,30 +1013,33 @@
         <v>125000</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E4" s="9">
         <v>15</v>
@@ -914,30 +1048,33 @@
         <v>350000</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E5" s="9">
         <v>10</v>
@@ -946,19 +1083,22 @@
         <v>250000</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -975,33 +1115,36 @@
         <v>8</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E7" s="9">
         <v>10</v>
@@ -1010,28 +1153,33 @@
         <v>250000</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>76</v>
+        <v>23</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="5"/>
-    </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" s="9">
         <v>15</v>
@@ -1040,30 +1188,33 @@
         <v>350000</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E9" s="9">
         <v>10</v>
@@ -1072,30 +1223,33 @@
         <v>250000</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E10" s="9">
         <v>10</v>
@@ -1104,242 +1258,269 @@
         <v>250000</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="E12" s="9">
+        <v>10</v>
+      </c>
+      <c r="F12" s="8">
+        <v>250000</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="9">
+        <v>10</v>
+      </c>
+      <c r="F13" s="8">
+        <v>250000</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="9">
         <v>15</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F14" s="8">
         <v>350000</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
-        <v>13</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="11" t="s">
+      <c r="G14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="I14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="9">
+        <v>7</v>
+      </c>
+      <c r="F15" s="8">
+        <v>150000</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="9">
-        <v>7</v>
-      </c>
-      <c r="F13" s="8">
-        <v>150000</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J13" s="5"/>
-    </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
-        <v>14</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="9">
+      <c r="C16" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="9">
         <v>5</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F16" s="8">
         <v>125000</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J14" s="5"/>
-    </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
-        <v>15</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="J15" s="5"/>
-    </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
-        <v>16</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="9">
-        <v>10</v>
-      </c>
-      <c r="F16" s="8">
-        <v>250000</v>
-      </c>
       <c r="G16" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="J16" s="5"/>
-    </row>
-    <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="9">
-        <v>10</v>
-      </c>
-      <c r="F17" s="8">
-        <v>250000</v>
+        <v>29</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="J17" s="5"/>
-    </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" s="9">
         <v>10</v>
@@ -1348,28 +1529,31 @@
         <v>250000</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J18" s="5"/>
-    </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K18" s="5"/>
+    </row>
+    <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E19" s="9">
         <v>5</v>
@@ -1378,28 +1562,31 @@
         <v>125000</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="J19" s="5"/>
-    </row>
-    <row r="20" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" s="9">
         <v>5</v>
@@ -1408,26 +1595,31 @@
         <v>125000</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="J20" s="5"/>
+        <v>54</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="K20" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" display="https://github.com/Roberto-0720/01_RCDesignSAP2000/releases/download/RCDesignSAP2000_V1.0/RCDesignSAP2000.zip" xr:uid="{FC6AFCF8-E931-4527-92B8-4368B3E75E9B}"/>
-    <hyperlink ref="J3" r:id="rId2" display="https://github.com/Roberto-0720/05_GroundFloorDesign/releases/download/GRDS_V1.1/GRDS.zip" xr:uid="{9BB3CC40-CC6A-4414-B050-E7514485A24B}"/>
-    <hyperlink ref="J6" r:id="rId3" display="https://github.com/Roberto-0720/05_GroundFloorDesign/releases/download/GRDS_V1.1/GRDS.zip" xr:uid="{E64AFE90-7C28-4CBA-8503-4E21282078F9}"/>
-    <hyperlink ref="J4" r:id="rId4" display="https://github.com/Roberto-0720/03_DeflectionCheck/releases/download/DeflectionCheck_V2.5/DeflectionCheck.zip" xr:uid="{3DD867BE-BA0D-438B-9050-E4DF6E02CAAF}"/>
-    <hyperlink ref="J5" r:id="rId5" display="https://github.com/Roberto-0720/04_PileCapacityCheck/releases/download/PileCapacityCheck_V1.2/PileCapcityCheck.zip" xr:uid="{41FA4F41-A17A-4013-8605-273E87099097}"/>
-    <hyperlink ref="J11" r:id="rId6" display="https://github.com/Roberto-0720/10_SeismicOnVerTank/releases/download/SeismicOnVerTank_V2.1/SeismicOnVerticalTank.zip" xr:uid="{D1F304C9-0739-4C19-97D6-1830521DFE31}"/>
-    <hyperlink ref="J10" r:id="rId7" display="https://github.com/Roberto-0720/09_WindLoadOnVerticalTank/releases/download/WindLoadOnVerTank_V2.1/WindLoadOnVerticalTank.zip" xr:uid="{5DC07B34-BEE5-4B8C-8206-B90F423026BC}"/>
-    <hyperlink ref="J9" r:id="rId8" display="https://github.com/Roberto-0720/08_MonorailBeamDesgin/releases/download/Monorail_V1.2/Monorail.zip" xr:uid="{4FF4D90B-241F-4E67-9DD3-9D3DB452E7E9}"/>
+    <hyperlink ref="K3" r:id="rId1" display="https://github.com/Roberto-0720/05_GroundFloorDesign/releases/download/GRDS_V1.1/GRDS.zip" xr:uid="{9BB3CC40-CC6A-4414-B050-E7514485A24B}"/>
+    <hyperlink ref="K6" r:id="rId2" display="https://github.com/Roberto-0720/05_GroundFloorDesign/releases/download/GRDS_V1.1/GRDS.zip" xr:uid="{E64AFE90-7C28-4CBA-8503-4E21282078F9}"/>
+    <hyperlink ref="K4" r:id="rId3" display="https://github.com/Roberto-0720/03_DeflectionCheck/releases/download/DeflectionCheck_V2.5/DeflectionCheck.zip" xr:uid="{3DD867BE-BA0D-438B-9050-E4DF6E02CAAF}"/>
+    <hyperlink ref="K5" r:id="rId4" display="https://github.com/Roberto-0720/04_PileCapacityCheck/releases/download/PileCapacityCheck_V1.2/PileCapcityCheck.zip" xr:uid="{41FA4F41-A17A-4013-8605-273E87099097}"/>
+    <hyperlink ref="K11" r:id="rId5" display="https://github.com/Roberto-0720/10_SeismicOnVerTank/releases/download/SeismicOnVerTank_V2.1/SeismicOnVerticalTank.zip" xr:uid="{D1F304C9-0739-4C19-97D6-1830521DFE31}"/>
+    <hyperlink ref="K10" r:id="rId6" display="https://github.com/Roberto-0720/09_WindLoadOnVerticalTank/releases/download/WindLoadOnVerTank_V2.1/WindLoadOnVerticalTank.zip" xr:uid="{5DC07B34-BEE5-4B8C-8206-B90F423026BC}"/>
+    <hyperlink ref="K9" r:id="rId7" display="https://github.com/Roberto-0720/08_MonorailBeamDesgin/releases/download/Monorail_V1.2/Monorail.zip" xr:uid="{4FF4D90B-241F-4E67-9DD3-9D3DB452E7E9}"/>
+    <hyperlink ref="K2" r:id="rId8" display="https://github.com/Roberto-0720/01_RCDesignSAP2000/releases/download/RCDesignSAP2000_V1.0/RCD.zip" xr:uid="{DE308F54-19C3-4D53-9A09-6BA1E30F28D6}"/>
+    <hyperlink ref="K13" r:id="rId9" display="https://github.com/Roberto-0720/10_SeismicOnVerTank/releases/download/SeismicOnVerTank_V2.1/SeismicOnVerticalTank.zip" xr:uid="{87A39533-709E-4538-8722-1A870042C899}"/>
+    <hyperlink ref="K12" r:id="rId10" display="https://github.com/Roberto-0720/09_WindLoadOnVerticalTank/releases/download/WindLoadOnVerTank_V2.1/WindLoadOnVerticalTank.zip" xr:uid="{AD99417B-CB6F-4F57-B59D-CC5FEAFCB42B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1435,229 +1627,312 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{829F40C7-2586-48ED-945E-E6E6E6261F80}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="3" width="39" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="39" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="1" customWidth="1"/>
+    <col min="4" max="7" width="16.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="18"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B3" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="4">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2">
+        <v>250000</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="1">
+        <f>+C3*25000</f>
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="4">
         <v>5</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="2"/>
+      <c r="D4" s="2">
+        <v>125000</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J4" s="1">
+        <f>+C4*25000</f>
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="4"/>
+      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="4"/>
+      <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="4"/>
+      <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="4"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="4"/>
+      <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="14"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="4"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="4"/>
+      <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="4"/>
+      <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="4"/>
+      <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="4"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="4"/>
+      <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="4"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="4"/>
+      <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="4"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="4"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="4"/>
+      <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="4"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="4"/>
+      <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="4"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="4"/>
+      <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="4"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="4"/>
+      <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:8" ht="19.05" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" ht="19.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:9" ht="19.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:H2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Resource/software_list/softwarelist.xlsx
+++ b/Resource/software_list/softwarelist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\12 Claude-Cowork\03 Projects\20260623_WebsiteRobertoStructural\WebsiteRobertoStructural\Resource\software_list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B80196-7657-4988-A220-FE2B8435D144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966DB4C4-AF3A-4E90-97CC-729005E44E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AD0764AB-2672-4561-8C21-7DE139ED03BB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{AD0764AB-2672-4561-8C21-7DE139ED03BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Python Tool" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="113">
   <si>
     <t>STT</t>
   </si>
@@ -142,9 +142,6 @@
     <t>BASE PLATE DESIGN (HINGE TYPE)</t>
   </si>
   <si>
-    <t>V2.2</t>
-  </si>
-  <si>
     <t>STAAD UNBRACED LENGTH CALCULATOR</t>
   </si>
   <si>
@@ -188,9 +185,6 @@
   </si>
   <si>
     <t>StaadULCalculator.exe</t>
-  </si>
-  <si>
-    <t>BasePlateDesign.exe</t>
   </si>
   <si>
     <t>Category</t>
@@ -323,6 +317,90 @@
   </si>
   <si>
     <t>Villa_01_12x20x2.5</t>
+  </si>
+  <si>
+    <t>Villa_02_10x10x2</t>
+  </si>
+  <si>
+    <t>Townhouse_02_5x19x4</t>
+  </si>
+  <si>
+    <t>Townhouse_03_5x20x4</t>
+  </si>
+  <si>
+    <t>Townhouse_04_6x20x4</t>
+  </si>
+  <si>
+    <t>Townhouse_05_4x21x4</t>
+  </si>
+  <si>
+    <t>Townhouse_06_4x20x4</t>
+  </si>
+  <si>
+    <t>Tuduong_01_9x11</t>
+  </si>
+  <si>
+    <t>BPL.exe</t>
+  </si>
+  <si>
+    <t>Test Again</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/13_BasePlateDesign/releases/download/BasePlateDesgin_V2.3/BPL.zip
+https://github.com/Roberto-0720/13_BasePlateDesign/releases/latest/downloadBPL.zip</t>
+  </si>
+  <si>
+    <t>EQUIPMENT ANCHOR BOLT DESIGN</t>
+  </si>
+  <si>
+    <t>EQAB.exe</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/20_EQAnchorBoltDesign/releases/download/EquipmentABDesignV1.1/EQAB.zip
+https://github.com/Roberto-0720/20_EQAnchorBoltDesign/releases/latest/download/EQAB.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/Townhouse_02_5x19x4/releases/download/Townhouse_02_5x19x4/5X19X4.zip
+https://github.com/Roberto-0720/Townhouse_02_5x19x4/releases/latest/download/5X19X4.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/Townhouse_03_5x20x4/releases/download/Townhouse_03_5x20x4/Townhouse_03_5x20x4.zip
+https://github.com/Roberto-0720/Townhouse_03_5x20x4/releases/latest/download/Townhouse_03_5x20x4.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/Townhouse_04_6x20x4/releases/download/Townhouse_04_6x20x4/6x20x4.zip
+https://github.com/Roberto-0720/Townhouse_04_6x20x4/releases/latest/download/6x20x4.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/Townhouse_05_4x21x4/releases/download/Townhouse_05_4x21x4/Townhouse_05_4x21x4.zip
+https://github.com/Roberto-0720/Townhouse_05_4x21x4/releases/latest/download/Townhouse_05_4x21x4.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/Townhouse_06_4x20x4/releases/download/Townhouse_06_4x20x4/Townhouse_06_4x20x4.zip
+https://github.com/Roberto-0720/Townhouse_06_4x20x4/releases/latest/download/Townhouse_06_4x20x4.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/Tuduong_01/releases/download/Tuduong_01/Tuduong_01_9x11.zip
+https://github.com/Roberto-0720/Tuduong_01/releases/latest/download/Tuduong_01_9x11.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/Villa_02_10x10x2/releases/download/Villa_02_10x10x2/Villa_02_10x10x2.zip
+https://github.com/Roberto-0720/Villa_02_10x10x2/releases/latest/download/Villa_02_10x10x2.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/Townhouse_01_5x14.5x4/releases/download/Townhouse_01_5x14.5x4/Townhouse_01_5x14.5x4.zip
+https://github.com/Roberto-0720/Townhouse_01_5x14.5x4/releases/latest/download/Townhouse_01_5x14.5x4.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/Villa_01_12x20x2.5/releases/download/Villa_01_12x20x2.5/Villa_01_12x20x2.5.zip
+https://github.com/Roberto-0720/Villa_01_12x20x2.5/releases/latest/download/Villa_01_12x20x2.5.zip</t>
+  </si>
+  <si>
+    <t>https://github.com/Roberto-0720/Tuduong_02_15x6.5/releases/download/Tuduong_02_15x6.5/Tuduong_02_15x6.5.dwg.zip
+https://github.com/Roberto-0720/Tuduong_02_15x6.5/releases/latest/download/Tuduong_02_15x6.5.dwg.zip</t>
+  </si>
+  <si>
+    <t>Tuduong_02_15x6.5</t>
   </si>
 </sst>
 </file>
@@ -332,7 +410,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;\-&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,11 +468,20 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Symbol"/>
-      <family val="1"/>
-      <charset val="2"/>
+      <u/>
+      <sz val="10"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -417,7 +504,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -503,12 +590,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -549,8 +658,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -566,6 +684,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -907,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2825F4-381A-4176-BB68-B1332D84AD9D}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.77734375" style="1" customWidth="1"/>
@@ -949,13 +1073,13 @@
         <v>31</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -966,7 +1090,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>12</v>
@@ -984,13 +1108,13 @@
         <v>32</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1001,7 +1125,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>14</v>
@@ -1019,13 +1143,13 @@
         <v>32</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1036,7 +1160,7 @@
         <v>15</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>16</v>
@@ -1054,13 +1178,13 @@
         <v>32</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1071,7 +1195,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>18</v>
@@ -1089,13 +1213,13 @@
         <v>32</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1124,13 +1248,13 @@
         <v>32</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1141,7 +1265,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>20</v>
@@ -1159,13 +1283,13 @@
         <v>32</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1194,13 +1318,13 @@
         <v>32</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1211,7 +1335,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>18</v>
@@ -1229,13 +1353,13 @@
         <v>32</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1246,7 +1370,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>29</v>
@@ -1264,13 +1388,13 @@
         <v>32</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1281,7 +1405,7 @@
         <v>30</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>29</v>
@@ -1299,13 +1423,13 @@
         <v>32</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1313,10 +1437,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>12</v>
@@ -1334,13 +1458,13 @@
         <v>32</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1348,10 +1472,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>12</v>
@@ -1369,13 +1493,13 @@
         <v>32</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1386,10 +1510,10 @@
         <v>33</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E14" s="9">
         <v>15</v>
@@ -1400,26 +1524,28 @@
       <c r="G14" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>59</v>
+      <c r="H14" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="K14" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>29</v>
@@ -1431,16 +1557,16 @@
         <v>150000</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K15" s="5"/>
     </row>
@@ -1449,10 +1575,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>20</v>
@@ -1467,13 +1593,13 @@
         <v>22</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K16" s="5"/>
     </row>
@@ -1482,10 +1608,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>29</v>
@@ -1500,13 +1626,13 @@
         <v>22</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1514,10 +1640,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>12</v>
@@ -1529,16 +1655,16 @@
         <v>250000</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K18" s="5"/>
     </row>
@@ -1547,10 +1673,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>42</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>43</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>29</v>
@@ -1565,13 +1691,13 @@
         <v>22</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K19" s="5"/>
     </row>
@@ -1580,10 +1706,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>45</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>12</v>
@@ -1598,15 +1724,50 @@
         <v>22</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K20" s="5"/>
+    </row>
+    <row r="21" spans="1:11" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="9">
+        <v>5</v>
+      </c>
+      <c r="F21" s="8">
+        <v>125000</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>101</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1620,6 +1781,8 @@
     <hyperlink ref="K2" r:id="rId8" display="https://github.com/Roberto-0720/01_RCDesignSAP2000/releases/download/RCDesignSAP2000_V1.0/RCD.zip" xr:uid="{DE308F54-19C3-4D53-9A09-6BA1E30F28D6}"/>
     <hyperlink ref="K13" r:id="rId9" display="https://github.com/Roberto-0720/10_SeismicOnVerTank/releases/download/SeismicOnVerTank_V2.1/SeismicOnVerticalTank.zip" xr:uid="{87A39533-709E-4538-8722-1A870042C899}"/>
     <hyperlink ref="K12" r:id="rId10" display="https://github.com/Roberto-0720/09_WindLoadOnVerticalTank/releases/download/WindLoadOnVerTank_V2.1/WindLoadOnVerticalTank.zip" xr:uid="{AD99417B-CB6F-4F57-B59D-CC5FEAFCB42B}"/>
+    <hyperlink ref="K21" r:id="rId11" display="https://github.com/Roberto-0720/09_WindLoadOnVerticalTank/releases/download/WindLoadOnVerTank_V2.1/WindLoadOnVerticalTank.zip" xr:uid="{C91B5D94-8301-40A3-82C0-D9DF625A0AD9}"/>
+    <hyperlink ref="K14" r:id="rId12" display="https://github.com/Roberto-0720/09_WindLoadOnVerticalTank/releases/download/WindLoadOnVerTank_V2.1/WindLoadOnVerticalTank.zip" xr:uid="{DF82DB5E-D85F-469E-9614-29229BE2E576}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1627,99 +1790,111 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{829F40C7-2586-48ED-945E-E6E6E6261F80}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="39" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.33203125" style="1" customWidth="1"/>
     <col min="4" max="7" width="16.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="14.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
+    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="99" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="21"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="18"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-    </row>
-    <row r="3" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="15"/>
+    </row>
+    <row r="3" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="4">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>125000</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="4">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2">
-        <v>250000</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J3" s="1">
-        <f>+C3*25000</f>
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C4" s="4">
         <v>5</v>
@@ -1728,113 +1903,293 @@
         <v>125000</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="1">
-        <f>+C4*25000</f>
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C5" s="4">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="4">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>125000</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="4">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="4">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
+        <v>125000</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
       <c r="B13" s="13"/>
       <c r="C13" s="4"/>
       <c r="D13" s="2"/>
@@ -1843,9 +2198,13 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:11" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
       <c r="B14" s="13"/>
       <c r="C14" s="4"/>
       <c r="D14" s="2"/>
@@ -1854,77 +2213,13 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9" ht="19.05" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:9" ht="19.05" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="J1:J2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
@@ -1933,6 +2228,10 @@
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:H2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="K6" r:id="rId1" display="https://github.com/Roberto-0720/Townhouse_02_5x19x4/releases/download/Townhouse_02_5x19x4/5X19X4.zip" xr:uid="{CCBD3C7C-1989-48C6-B715-67A1FDCC1C8A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>